--- a/Estado_Processos_Recebimento.xlsx
+++ b/Estado_Processos_Recebimento.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,49 +460,203 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>TOTAL_ADIANTADO_COMISSAO</t>
+          <t>SALDO_A_RECEBER</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>TOTAL_COMISSAO_ANTECIPACOES</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL_COMISSAO_REGULARES</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL_COMISSAO_ACUMULADA</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>STATUS_PROCESSO</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>STATUS_PAGAMENTO</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>STATUS_CALCULO_MEDIAS</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>MES_ANO_FATURAMENTO</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TCMP_JSON</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>FCMP_JSON</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TCMP_DETALHES_JSON</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>FCMP_DETALHES_JSON</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>COLABORADORES_ENVOLVIDOS</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>DATA_PRIMEIRO_PAGAMENTO</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>DATA_ULTIMO_PAGAMENTO</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>QUANTIDADE_PAGAMENTOS</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ULTIMA_ATUALIZACAO</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>COMISSOES_ADIANTADAS_JSON</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>STATUS_RECONCILIACAO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>STATUS_PROCESSO_ANALISE</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>STATUS_CALCULO_MEDIAS</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>MES_ANO_FATURAMENTO</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>TCMP</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>FCMP</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>ULTIMA_ATUALIZACAO</t>
-        </is>
-      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OBSERVACOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>100002</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>70</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1274285714285714</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1274285714285714</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>FATURADO</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CALCULADO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>{"Alessandro Cappi": 0.010000000000000002}</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{"Alessandro Cappi": 0.3185714285714285}</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 0.362, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 120.0, "meta": 100.0, "atingimento": 1.2, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 20.0, "meta": 100.0, "atingimento": 0.2, "atingimento_cap": 0.2, "componente_fc": 0.06}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.38, "meta": 0.5, "atingimento": 0.76, "atingimento_cap": 0.76, "componente_fc": 0.15200000000000002}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 66.66666666666667, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.362}}, {"negocio": "SSO", "grupo": "Detector Fixo", "subgrupo": "XCD", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.21, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 120.0, "meta": 100.0, "atingimento": 1.2, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 20.0, "meta": 100.0, "atingimento": 0.2, "atingimento_cap": 0.2, "componente_fc": 0.06}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.0, "meta": 0.5, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 66.66666666666667, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.21}}], "total_valor": 70.0, "soma_ponderada": 0.7000000000000002, "tcmp_final": 0.010000000000000002}}</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 0.362, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 120.0, "meta": 100.0, "atingimento": 1.2, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 20.0, "meta": 100.0, "atingimento": 0.2, "atingimento_cap": 0.2, "componente_fc": 0.06}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.38, "meta": 0.5, "atingimento": 0.76, "atingimento_cap": 0.76, "componente_fc": 0.15200000000000002}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 66.66666666666667, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.362}}, {"negocio": "SSO", "grupo": "Detector Fixo", "subgrupo": "XCD", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.21, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 120.0, "meta": 100.0, "atingimento": 1.2, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 20.0, "meta": 100.0, "atingimento": 0.2, "atingimento_cap": 0.2, "componente_fc": 0.06}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.0, "meta": 0.5, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 66.66666666666667, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.21}}], "total_valor": 70.0, "soma_ponderada": 22.299999999999997, "fcmp_final": 0.3185714285714285}}</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Alessandro Cappi</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>45994.69888204768</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Estado_Processos_Recebimento.xlsx
+++ b/Estado_Processos_Recebimento.xlsx
@@ -562,20 +562,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>100002</t>
+          <t>100001</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
         <v>30</v>
@@ -584,10 +584,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1274285714285714</v>
+        <v>0.06340000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1274285714285714</v>
+        <v>0.06340000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -616,17 +616,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{"Alessandro Cappi": 0.3185714285714285}</t>
+          <t>{"Alessandro Cappi": 0.317}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 0.362, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 120.0, "meta": 100.0, "atingimento": 1.2, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 20.0, "meta": 100.0, "atingimento": 0.2, "atingimento_cap": 0.2, "componente_fc": 0.06}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.38, "meta": 0.5, "atingimento": 0.76, "atingimento_cap": 0.76, "componente_fc": 0.15200000000000002}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 66.66666666666667, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.362}}, {"negocio": "SSO", "grupo": "Detector Fixo", "subgrupo": "XCD", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.21, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 120.0, "meta": 100.0, "atingimento": 1.2, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 20.0, "meta": 100.0, "atingimento": 0.2, "atingimento_cap": 0.2, "componente_fc": 0.06}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.0, "meta": 0.5, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 66.66666666666667, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.21}}], "total_valor": 70.0, "soma_ponderada": 0.7000000000000002, "tcmp_final": 0.010000000000000002}}</t>
+          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 0.317, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 70.0, "meta": 100.0, "atingimento": 0.7, "atingimento_cap": 0.7, "componente_fc": 0.105}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 20.0, "meta": 100.0, "atingimento": 0.2, "atingimento_cap": 0.2, "componente_fc": 0.06}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.38, "meta": 0.5, "atingimento": 0.76, "atingimento_cap": 0.76, "componente_fc": 0.15200000000000002}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 66.66666666666667, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.317}}], "total_valor": 50.0, "soma_ponderada": 0.5000000000000001, "tcmp_final": 0.010000000000000002}}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 0.362, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 120.0, "meta": 100.0, "atingimento": 1.2, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 20.0, "meta": 100.0, "atingimento": 0.2, "atingimento_cap": 0.2, "componente_fc": 0.06}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.38, "meta": 0.5, "atingimento": 0.76, "atingimento_cap": 0.76, "componente_fc": 0.15200000000000002}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 66.66666666666667, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.362}}, {"negocio": "SSO", "grupo": "Detector Fixo", "subgrupo": "XCD", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.21, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 120.0, "meta": 100.0, "atingimento": 1.2, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 20.0, "meta": 100.0, "atingimento": 0.2, "atingimento_cap": 0.2, "componente_fc": 0.06}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.0, "meta": 0.5, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 66.66666666666667, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.21}}], "total_valor": 70.0, "soma_ponderada": 22.299999999999997, "fcmp_final": 0.3185714285714285}}</t>
+          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 0.317, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 70.0, "meta": 100.0, "atingimento": 0.7, "atingimento_cap": 0.7, "componente_fc": 0.105}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 20.0, "meta": 100.0, "atingimento": 0.2, "atingimento_cap": 0.2, "componente_fc": 0.06}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.38, "meta": 0.5, "atingimento": 0.76, "atingimento_cap": 0.76, "componente_fc": 0.15200000000000002}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 66.66666666666667, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.317}}], "total_valor": 50.0, "soma_ponderada": 15.85, "fcmp_final": 0.317}}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="S2" s="2" t="n">
-        <v>45897</v>
+        <v>45879</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>45897</v>
+        <v>45879</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>45994.69888204768</v>
+        <v>45995.63094627377</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>

--- a/Estado_Processos_Recebimento.xlsx
+++ b/Estado_Processos_Recebimento.xlsx
@@ -562,36 +562,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>100001</t>
+          <t>100002</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
-        <v>20</v>
-      </c>
       <c r="E2" t="n">
-        <v>20</v>
-      </c>
-      <c r="F2" t="n">
-        <v>30</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>0.06340000000000001</v>
-      </c>
       <c r="I2" t="n">
-        <v>0.06340000000000001</v>
+        <v>10</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>FATURADO</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -601,14 +599,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CALCULADO</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>08/2025</t>
-        </is>
-      </c>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>{"Alessandro Cappi": 0.010000000000000002}</t>
@@ -616,17 +610,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{"Alessandro Cappi": 0.317}</t>
+          <t>{"Alessandro Cappi": 1.0}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 0.317, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 70.0, "meta": 100.0, "atingimento": 0.7, "atingimento_cap": 0.7, "componente_fc": 0.105}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 20.0, "meta": 100.0, "atingimento": 0.2, "atingimento_cap": 0.2, "componente_fc": 0.06}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.38, "meta": 0.5, "atingimento": 0.76, "atingimento_cap": 0.76, "componente_fc": 0.15200000000000002}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 66.66666666666667, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.317}}], "total_valor": 50.0, "soma_ponderada": 0.5000000000000001, "tcmp_final": 0.010000000000000002}}</t>
+          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 5000.0, "taxa": 0.010000000000000002, "fc": 1.0, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": null}], "total_valor": 5000.0, "soma_ponderada": 50.00000000000001, "tcmp_final": 0.010000000000000002}}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 0.317, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 70.0, "meta": 100.0, "atingimento": 0.7, "atingimento_cap": 0.7, "componente_fc": 0.105}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 20.0, "meta": 100.0, "atingimento": 0.2, "atingimento_cap": 0.2, "componente_fc": 0.06}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.38, "meta": 0.5, "atingimento": 0.76, "atingimento_cap": 0.76, "componente_fc": 0.15200000000000002}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 66.66666666666667, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.317}}], "total_valor": 50.0, "soma_ponderada": 15.85, "fcmp_final": 0.317}}</t>
+          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 5000.0, "taxa": 0.010000000000000002, "fc": 1.0, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": null}], "total_valor": 5000.0, "soma_ponderada": 5000.0, "fcmp_final": 1.0}}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -635,20 +629,20 @@
         </is>
       </c>
       <c r="S2" s="2" t="n">
-        <v>45879</v>
+        <v>45870</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>45879</v>
+        <v>45870</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>45995.63094627377</v>
+        <v>46000.5783992941</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"Alessandro Cappi": 10.000000000000002}</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">

--- a/Estado_Processos_Recebimento.xlsx
+++ b/Estado_Processos_Recebimento.xlsx
@@ -562,47 +562,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>100002</t>
+          <t>100001</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>10</v>
-      </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>FATURADO</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
+          <t>COMPLETO</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>CALCULADO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>08/2025</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>{"Alessandro Cappi": 0.010000000000000002}</t>
@@ -615,12 +621,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 5000.0, "taxa": 0.010000000000000002, "fc": 1.0, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": null}], "total_valor": 5000.0, "soma_ponderada": 50.00000000000001, "tcmp_final": 0.010000000000000002}}</t>
+          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 1.0, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": null}], "total_valor": 50.0, "soma_ponderada": 0.5000000000000001, "tcmp_final": 0.010000000000000002}}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 5000.0, "taxa": 0.010000000000000002, "fc": 1.0, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": null}], "total_valor": 5000.0, "soma_ponderada": 5000.0, "fcmp_final": 1.0}}</t>
+          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 1.0, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": null}], "total_valor": 50.0, "soma_ponderada": 50.0, "fcmp_final": 1.0}}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -629,20 +635,20 @@
         </is>
       </c>
       <c r="S2" s="2" t="n">
-        <v>45870</v>
+        <v>45879</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>45870</v>
+        <v>45879</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>46000.5783992941</v>
+        <v>46001.54534326905</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>{"Alessandro Cappi": 10.000000000000002}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">

--- a/Estado_Processos_Recebimento.xlsx
+++ b/Estado_Processos_Recebimento.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,7 +562,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>100001</t>
+          <t>TESTE</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -572,22 +572,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.2016</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.2016</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -596,67 +596,166 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>CALCULADO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>{"André Caramello": 0.010000000000000002}</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>{"André Caramello": 0.504}</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.52, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 0.0, "atingimento": 1.0, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.52}}, {"negocio": "Hidrologia", "grupo": "Medidor de Vazão Fixo", "subgrupo": "IQ Standard", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.48, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.3, "meta": 0.5, "atingimento": 0.6, "atingimento_cap": 0.6, "componente_fc": 0.12}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 0.0, "atingimento": 1.0, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.48}}], "total_valor": 50.0, "soma_ponderada": 0.5000000000000001, "tcmp_final": 0.010000000000000002}}</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.52, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 0.0, "atingimento": 1.0, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.52}}, {"negocio": "Hidrologia", "grupo": "Medidor de Vazão Fixo", "subgrupo": "IQ Standard", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.48, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.3, "meta": 0.5, "atingimento": 0.6, "atingimento_cap": 0.6, "componente_fc": 0.12}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 0.0, "atingimento": 1.0, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.48}}], "total_valor": 50.0, "soma_ponderada": 25.200000000000003, "fcmp_final": 0.504}}</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>André Caramello</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>46003.73082676124</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TESTE2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>FATURADO</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>COMPLETO</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>CALCULADO</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>08/2025</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>{"Alessandro Cappi": 0.010000000000000002}</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>{"Alessandro Cappi": 1.0}</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 1.0, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": null}], "total_valor": 50.0, "soma_ponderada": 0.5000000000000001, "tcmp_final": 0.010000000000000002}}</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{"Alessandro Cappi": {"itens": [{"negocio": "SSO", "grupo": "Detector Portátil", "subgrupo": "MicroClip", "tipo_mercadoria": "Produto", "valor": 50.0, "taxa": 0.010000000000000002, "fc": 1.0, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": null}], "total_valor": 50.0, "soma_ponderada": 50.0, "fcmp_final": 1.0}}</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Alessandro Cappi</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45879</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>45879</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>46001.54534326905</v>
-      </c>
-      <c r="W2" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>10/2025</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>{"André Caramello": 0.010000000000000002}</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>{"André Caramello": 0.52}</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.52, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 0.0, "atingimento": 1.0, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.52}}], "total_valor": 30.0, "soma_ponderada": 0.30000000000000004, "tcmp_final": 0.010000000000000002}}</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.52, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 0.0, "atingimento": 1.0, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.52}}], "total_valor": 30.0, "soma_ponderada": 15.600000000000001, "fcmp_final": 0.52}}</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>André Caramello</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>46003.73082856982</v>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>PENDENTE</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Estado_Processos_Recebimento.xlsx
+++ b/Estado_Processos_Recebimento.xlsx
@@ -584,10 +584,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2016</v>
+        <v>0.1816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2016</v>
+        <v>0.1816</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -616,17 +616,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{"André Caramello": 0.504}</t>
+          <t>{"André Caramello": 0.4539999999999999}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.52, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 0.0, "atingimento": 1.0, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.52}}, {"negocio": "Hidrologia", "grupo": "Medidor de Vazão Fixo", "subgrupo": "IQ Standard", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.48, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.3, "meta": 0.5, "atingimento": 0.6, "atingimento_cap": 0.6, "componente_fc": 0.12}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 0.0, "atingimento": 1.0, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.48}}], "total_valor": 50.0, "soma_ponderada": 0.5000000000000001, "tcmp_final": 0.010000000000000002}}</t>
+          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.47, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.641599999999999, "meta": 25.0, "atingimento": 0.585664, "atingimento_cap": 0.585664, "componente_fc": 0.0585664}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.47}}, {"negocio": "Hidrologia", "grupo": "Medidor de Vazão Fixo", "subgrupo": "IQ Standard", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.42999999999999994, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.3, "meta": 0.5, "atingimento": 0.6, "atingimento_cap": 0.6, "componente_fc": 0.12}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.641599999999999, "meta": 25.0, "atingimento": 0.585664, "atingimento_cap": 0.585664, "componente_fc": 0.0585664}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.42999999999999994}}], "total_valor": 50.0, "soma_ponderada": 0.5000000000000001, "tcmp_final": 0.010000000000000002}}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.52, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 0.0, "atingimento": 1.0, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.52}}, {"negocio": "Hidrologia", "grupo": "Medidor de Vazão Fixo", "subgrupo": "IQ Standard", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.48, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.3, "meta": 0.5, "atingimento": 0.6, "atingimento_cap": 0.6, "componente_fc": 0.12}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 0.0, "atingimento": 1.0, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.48}}], "total_valor": 50.0, "soma_ponderada": 25.200000000000003, "fcmp_final": 0.504}}</t>
+          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.47, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.641599999999999, "meta": 25.0, "atingimento": 0.585664, "atingimento_cap": 0.585664, "componente_fc": 0.0585664}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.47}}, {"negocio": "Hidrologia", "grupo": "Medidor de Vazão Fixo", "subgrupo": "IQ Standard", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.42999999999999994, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.3, "meta": 0.5, "atingimento": 0.6, "atingimento_cap": 0.6, "componente_fc": 0.12}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.641599999999999, "meta": 25.0, "atingimento": 0.585664, "atingimento_cap": 0.585664, "componente_fc": 0.0585664}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.42999999999999994}}], "total_valor": 50.0, "soma_ponderada": 22.699999999999996, "fcmp_final": 0.4539999999999999}}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>46003.73082676124</v>
+        <v>46006.50389604088</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -683,10 +683,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.156</v>
+        <v>0.141</v>
       </c>
       <c r="I3" t="n">
-        <v>0.156</v>
+        <v>0.141</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -715,17 +715,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{"André Caramello": 0.52}</t>
+          <t>{"André Caramello": 0.47}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.52, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 0.0, "atingimento": 1.0, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.52}}], "total_valor": 30.0, "soma_ponderada": 0.30000000000000004, "tcmp_final": 0.010000000000000002}}</t>
+          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.47, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.641599999999999, "meta": 25.0, "atingimento": 0.585664, "atingimento_cap": 0.585664, "componente_fc": 0.0585664}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.47}}], "total_valor": 30.0, "soma_ponderada": 0.30000000000000004, "tcmp_final": 0.010000000000000002}}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.52, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 0.0, "atingimento": 1.0, "atingimento_cap": 1.0, "componente_fc": 0.15}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.52}}], "total_valor": 30.0, "soma_ponderada": 15.600000000000001, "fcmp_final": 0.52}}</t>
+          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.47, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.641599999999999, "meta": 25.0, "atingimento": 0.585664, "atingimento_cap": 0.585664, "componente_fc": 0.0585664}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.47}}], "total_valor": 30.0, "soma_ponderada": 14.1, "fcmp_final": 0.47}}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>46003.73082856982</v>
+        <v>46006.50389731903</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>

--- a/Estado_Processos_Recebimento.xlsx
+++ b/Estado_Processos_Recebimento.xlsx
@@ -621,12 +621,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.47, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.641599999999999, "meta": 25.0, "atingimento": 0.585664, "atingimento_cap": 0.585664, "componente_fc": 0.0585664}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.47}}, {"negocio": "Hidrologia", "grupo": "Medidor de Vazão Fixo", "subgrupo": "IQ Standard", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.42999999999999994, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.3, "meta": 0.5, "atingimento": 0.6, "atingimento_cap": 0.6, "componente_fc": 0.12}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.641599999999999, "meta": 25.0, "atingimento": 0.585664, "atingimento_cap": 0.585664, "componente_fc": 0.0585664}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.42999999999999994}}], "total_valor": 50.0, "soma_ponderada": 0.5000000000000001, "tcmp_final": 0.010000000000000002}}</t>
+          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.47, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.85573769241505, "meta": 25.0, "atingimento": 0.594229507696602, "atingimento_cap": 0.594229507696602, "componente_fc": 0.0594229507696602}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.47}}, {"negocio": "Hidrologia", "grupo": "Medidor de Vazão Fixo", "subgrupo": "IQ Standard", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.42999999999999994, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.3, "meta": 0.5, "atingimento": 0.6, "atingimento_cap": 0.6, "componente_fc": 0.12}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.85573769241505, "meta": 25.0, "atingimento": 0.594229507696602, "atingimento_cap": 0.594229507696602, "componente_fc": 0.0594229507696602}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.42999999999999994}}], "total_valor": 50.0, "soma_ponderada": 0.5000000000000001, "tcmp_final": 0.010000000000000002}}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.47, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.641599999999999, "meta": 25.0, "atingimento": 0.585664, "atingimento_cap": 0.585664, "componente_fc": 0.0585664}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.47}}, {"negocio": "Hidrologia", "grupo": "Medidor de Vazão Fixo", "subgrupo": "IQ Standard", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.42999999999999994, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.3, "meta": 0.5, "atingimento": 0.6, "atingimento_cap": 0.6, "componente_fc": 0.12}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.641599999999999, "meta": 25.0, "atingimento": 0.585664, "atingimento_cap": 0.585664, "componente_fc": 0.0585664}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.42999999999999994}}], "total_valor": 50.0, "soma_ponderada": 22.699999999999996, "fcmp_final": 0.4539999999999999}}</t>
+          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.47, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.85573769241505, "meta": 25.0, "atingimento": 0.594229507696602, "atingimento_cap": 0.594229507696602, "componente_fc": 0.0594229507696602}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.47}}, {"negocio": "Hidrologia", "grupo": "Medidor de Vazão Fixo", "subgrupo": "IQ Standard", "tipo_mercadoria": "Produto", "valor": 20.0, "taxa": 0.010000000000000002, "fc": 0.42999999999999994, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.3, "meta": 0.5, "atingimento": 0.6, "atingimento_cap": 0.6, "componente_fc": 0.12}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.85573769241505, "meta": 25.0, "atingimento": 0.594229507696602, "atingimento_cap": 0.594229507696602, "componente_fc": 0.0594229507696602}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.42999999999999994}}], "total_valor": 50.0, "soma_ponderada": 22.699999999999996, "fcmp_final": 0.4539999999999999}}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>46006.50389604088</v>
+        <v>46009.57911241149</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -720,12 +720,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.47, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.641599999999999, "meta": 25.0, "atingimento": 0.585664, "atingimento_cap": 0.585664, "componente_fc": 0.0585664}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.47}}], "total_valor": 30.0, "soma_ponderada": 0.30000000000000004, "tcmp_final": 0.010000000000000002}}</t>
+          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.47, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.85573769241505, "meta": 25.0, "atingimento": 0.594229507696602, "atingimento_cap": 0.594229507696602, "componente_fc": 0.0594229507696602}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.47}}], "total_valor": 30.0, "soma_ponderada": 0.30000000000000004, "tcmp_final": 0.010000000000000002}}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.47, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.641599999999999, "meta": 25.0, "atingimento": 0.585664, "atingimento_cap": 0.585664, "componente_fc": 0.0585664}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.47}}], "total_valor": 30.0, "soma_ponderada": 14.1, "fcmp_final": 0.47}}</t>
+          <t>{"André Caramello": {"itens": [{"negocio": "Hidrologia", "grupo": "Sonda Serie EXO", "subgrupo": "EXO", "tipo_mercadoria": "Produto", "valor": 30.0, "taxa": 0.010000000000000002, "fc": 0.47, "taxa_rateio": 0.05, "fatia_cargo": 0.2, "fc_detalhes": {"componentes": [{"nome_meta": "Faturamento da Linha", "peso": 0.15, "realizado": 80.0, "meta": 100.0, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.12}, {"nome_meta": "Conversão da Linha", "peso": 0.3, "realizado": 30.0, "meta": 100.0, "atingimento": 0.3, "atingimento_cap": 0.3, "componente_fc": 0.09}, {"nome_meta": "Rentabilidade", "peso": 0.2, "realizado": 0.4, "meta": 0.5, "atingimento": 0.8, "atingimento_cap": 0.8, "componente_fc": 0.16000000000000003}, {"nome_meta": "Retenção de Clientes", "peso": 0.15, "realizado": 2.0, "meta": 3.0, "atingimento": 0.6666666666666666, "atingimento_cap": 0.6666666666666666, "componente_fc": 0.09999999999999999}, {"nome_meta": "Meta Fornecedor 1", "peso": 0.1, "realizado": 14.85573769241505, "meta": 25.0, "atingimento": 0.594229507696602, "atingimento_cap": 0.594229507696602, "componente_fc": 0.0594229507696602}, {"nome_meta": "Meta Fornecedor 2", "peso": 0.1, "realizado": 0.0, "meta": 25.0, "atingimento": 0.0, "atingimento_cap": 0.0, "componente_fc": 0.0}], "fc_total": 0.47}}], "total_valor": 30.0, "soma_ponderada": 14.1, "fcmp_final": 0.47}}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>46006.50389731903</v>
+        <v>46009.57911319842</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>

--- a/Estado_Processos_Recebimento.xlsx
+++ b/Estado_Processos_Recebimento.xlsx
@@ -572,22 +572,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>-70</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1816</v>
+        <v>0.5448</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1816</v>
+        <v>0.5448</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PARCIAL</t>
+          <t>COMPLETO</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -641,10 +641,10 @@
         <v>45945</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>46009.57911241149</v>
+        <v>46010.42068233738</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -671,22 +671,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.141</v>
+        <v>0.423</v>
       </c>
       <c r="I3" t="n">
-        <v>0.141</v>
+        <v>0.423</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>45950</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>46009.57911319842</v>
+        <v>46010.42068246967</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>

--- a/Estado_Processos_Recebimento.xlsx
+++ b/Estado_Processos_Recebimento.xlsx
@@ -572,22 +572,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F2" t="n">
-        <v>-70</v>
+        <v>-150</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5448</v>
+        <v>0.9079999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5448</v>
+        <v>0.9079999999999999</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -641,10 +641,10 @@
         <v>45945</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>46010.42068233738</v>
+        <v>46010.47669455691</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -671,22 +671,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F3" t="n">
-        <v>-60</v>
+        <v>-120</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.423</v>
+        <v>0.7050000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.423</v>
+        <v>0.7050000000000001</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>45950</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>46010.42068246967</v>
+        <v>46010.47669473911</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>

--- a/Estado_Processos_Recebimento.xlsx
+++ b/Estado_Processos_Recebimento.xlsx
@@ -572,22 +572,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>-150</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9079999999999999</v>
+        <v>0.1816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9079999999999999</v>
+        <v>0.1816</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>COMPLETO</t>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -641,10 +641,10 @@
         <v>45945</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>46010.47669455691</v>
+        <v>46028.9608713977</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -671,22 +671,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7050000000000001</v>
+        <v>0.141</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7050000000000001</v>
+        <v>0.141</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>45950</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>46010.47669473911</v>
+        <v>46028.9608732295</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>

--- a/Estado_Processos_Recebimento.xlsx
+++ b/Estado_Processos_Recebimento.xlsx
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>46049.71458495028</v>
+        <v>46070.97325991028</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>46049.71458630793</v>
+        <v>46070.97326020588</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>

--- a/Estado_Processos_Recebimento.xlsx
+++ b/Estado_Processos_Recebimento.xlsx
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>46070.97325991028</v>
+        <v>46072.61991042176</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>46070.97326020588</v>
+        <v>46072.61991158671</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
